--- a/experiments/20250717_more_SOBOL/iteration_0/raw_data/raw_absorbance_i0.xlsx
+++ b/experiments/20250717_more_SOBOL/iteration_0/raw_data/raw_absorbance_i0.xlsx
@@ -2,22 +2,22 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Surfactant\0716\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Surfactant\0717\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6A9BC1E-DE8A-4189-B418-AEDE51173B39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B05A833F-05BB-4A33-80B9-C8ED21D6336D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1500" windowWidth="9528" windowHeight="10356"/>
   </bookViews>
   <sheets>
-    <sheet name="Plate 3 - Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Plate 1 - Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MethodPointer1">-555416336</definedName>
-    <definedName name="MethodPointer2">296</definedName>
+    <definedName name="MethodPointer1">2103747712</definedName>
+    <definedName name="MethodPointer2">558</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +46,7 @@
     <t>Experiment File Path:</t>
   </si>
   <si>
-    <t>D:\Surfactant\0716\ot-0.xpt</t>
+    <t>D:\Surfactant\0717\ot-0.xpt</t>
   </si>
   <si>
     <t>Protocol File Path:</t>
@@ -55,7 +55,7 @@
     <t>Plate Number</t>
   </si>
   <si>
-    <t>Plate 3</t>
+    <t>Plate 1</t>
   </si>
   <si>
     <t>Date</t>
@@ -97,7 +97,7 @@
     <t>Absorbance Endpoint</t>
   </si>
   <si>
-    <t>A1..B12</t>
+    <t>Full Plate</t>
   </si>
   <si>
     <t>Wavelengths:  600</t>
@@ -172,7 +172,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -193,7 +193,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF8DBCE0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7EB2DB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9CC5E5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABCEEA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAD7EF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF5197CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8E9F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC9E0F4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -205,13 +247,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF60A0D1"/>
+        <fgColor rgb="FF3385C2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF428EC7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -243,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="19" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -265,16 +307,37 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -305,39 +368,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -389,7 +452,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -500,13 +563,6 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -515,6 +571,13 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -579,13 +642,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
@@ -632,7 +710,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>45854</v>
+        <v>45855</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -640,7 +718,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2">
-        <v>0.49123842592592593</v>
+        <v>0.64116898148148149</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -720,7 +798,7 @@
         <v>24</v>
       </c>
       <c r="B22">
-        <v>22.7</v>
+        <v>24.7</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -767,42 +845,42 @@
         <v>25</v>
       </c>
       <c r="C25" s="7">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="D25" s="8">
-        <v>1.4379999999999999</v>
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="D25" s="7">
+        <v>0.16200000000000001</v>
       </c>
       <c r="E25" s="8">
-        <v>1.4790000000000001</v>
+        <v>1.3720000000000001</v>
       </c>
       <c r="F25" s="7">
-        <v>4.2000000000000003E-2</v>
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="G25" s="7">
         <v>0.04</v>
       </c>
       <c r="H25" s="7">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="I25" s="7">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="J25" s="7">
-        <v>6.9000000000000006E-2</v>
-      </c>
-      <c r="K25" s="7">
-        <v>6.5000000000000002E-2</v>
-      </c>
-      <c r="L25" s="7">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="M25" s="7">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="N25" s="7">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="O25" s="9">
+        <v>3.9E-2</v>
+      </c>
+      <c r="I25" s="8">
+        <v>1.512</v>
+      </c>
+      <c r="J25" s="8">
+        <v>1.399</v>
+      </c>
+      <c r="K25" s="9">
+        <v>1.538</v>
+      </c>
+      <c r="L25" s="10">
+        <v>1.1879999999999999</v>
+      </c>
+      <c r="M25" s="11">
+        <v>0.94899999999999995</v>
+      </c>
+      <c r="N25" s="12">
+        <v>0.877</v>
+      </c>
+      <c r="O25" s="13">
         <v>600</v>
       </c>
     </row>
@@ -810,17 +888,17 @@
       <c r="B26" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C26" s="10">
-        <v>1.891</v>
-      </c>
-      <c r="D26" s="11">
-        <v>1.339</v>
-      </c>
-      <c r="E26" s="11">
-        <v>1.2809999999999999</v>
+      <c r="C26" s="14">
+        <v>2.3580000000000001</v>
+      </c>
+      <c r="D26" s="15">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="E26" s="7">
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="F26" s="7">
-        <v>0.104</v>
+        <v>0.04</v>
       </c>
       <c r="G26" s="7">
         <v>0.04</v>
@@ -828,25 +906,25 @@
       <c r="H26" s="7">
         <v>3.9E-2</v>
       </c>
-      <c r="I26" s="7">
-        <v>3.9E-2</v>
-      </c>
-      <c r="J26" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="K26" s="7">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="L26" s="7">
-        <v>5.3999999999999999E-2</v>
-      </c>
-      <c r="M26" s="7">
-        <v>6.6000000000000003E-2</v>
-      </c>
-      <c r="N26" s="7">
-        <v>6.6000000000000003E-2</v>
-      </c>
-      <c r="O26" s="9">
+      <c r="I26" s="12">
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="J26" s="15">
+        <v>0.35099999999999998</v>
+      </c>
+      <c r="K26" s="15">
+        <v>0.42099999999999999</v>
+      </c>
+      <c r="L26" s="16">
+        <v>0.52100000000000002</v>
+      </c>
+      <c r="M26" s="16">
+        <v>0.58599999999999997</v>
+      </c>
+      <c r="N26" s="15">
+        <v>0.45300000000000001</v>
+      </c>
+      <c r="O26" s="13">
         <v>600</v>
       </c>
     </row>
@@ -854,19 +932,43 @@
       <c r="B27" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
-      <c r="K27" s="12"/>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="9">
+      <c r="C27" s="7">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="D27" s="7">
+        <v>0.17399999999999999</v>
+      </c>
+      <c r="E27" s="11">
+        <v>1.0089999999999999</v>
+      </c>
+      <c r="F27" s="7">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="G27" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="H27" s="7">
+        <v>3.9E-2</v>
+      </c>
+      <c r="I27" s="17">
+        <v>2.9009999999999998</v>
+      </c>
+      <c r="J27" s="17">
+        <v>2.87</v>
+      </c>
+      <c r="K27" s="18">
+        <v>2.7410000000000001</v>
+      </c>
+      <c r="L27" s="7">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="M27" s="10">
+        <v>1.3</v>
+      </c>
+      <c r="N27" s="8">
+        <v>1.3129999999999999</v>
+      </c>
+      <c r="O27" s="13">
         <v>600</v>
       </c>
     </row>
@@ -874,19 +976,43 @@
       <c r="B28" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="12"/>
-      <c r="J28" s="12"/>
-      <c r="K28" s="12"/>
-      <c r="L28" s="12"/>
-      <c r="M28" s="12"/>
-      <c r="N28" s="12"/>
-      <c r="O28" s="9">
+      <c r="C28" s="12">
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="D28" s="15">
+        <v>0.36299999999999999</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0.31900000000000001</v>
+      </c>
+      <c r="F28" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="G28" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="H28" s="7">
+        <v>3.9E-2</v>
+      </c>
+      <c r="I28" s="15">
+        <v>0.373</v>
+      </c>
+      <c r="J28" s="16">
+        <v>0.53100000000000003</v>
+      </c>
+      <c r="K28" s="12">
+        <v>0.70599999999999996</v>
+      </c>
+      <c r="L28" s="19">
+        <v>2.4009999999999998</v>
+      </c>
+      <c r="M28" s="14">
+        <v>2.2360000000000002</v>
+      </c>
+      <c r="N28" s="14">
+        <v>2.2429999999999999</v>
+      </c>
+      <c r="O28" s="13">
         <v>600</v>
       </c>
     </row>
@@ -894,19 +1020,43 @@
       <c r="B29" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="12"/>
-      <c r="J29" s="12"/>
-      <c r="K29" s="12"/>
-      <c r="L29" s="12"/>
-      <c r="M29" s="12"/>
-      <c r="N29" s="12"/>
-      <c r="O29" s="9">
+      <c r="C29" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="D29" s="7">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="E29" s="7">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="F29" s="7">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="G29" s="7">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="H29" s="7">
+        <v>3.9E-2</v>
+      </c>
+      <c r="I29" s="7">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="J29" s="7">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="K29" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="L29" s="10">
+        <v>1.2470000000000001</v>
+      </c>
+      <c r="M29" s="8">
+        <v>1.3939999999999999</v>
+      </c>
+      <c r="N29" s="10">
+        <v>1.248</v>
+      </c>
+      <c r="O29" s="13">
         <v>600</v>
       </c>
     </row>
@@ -914,19 +1064,43 @@
       <c r="B30" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="12"/>
-      <c r="J30" s="12"/>
-      <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
-      <c r="M30" s="12"/>
-      <c r="N30" s="12"/>
-      <c r="O30" s="9">
+      <c r="C30" s="7">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="D30" s="7">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="E30" s="7">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="F30" s="7">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="G30" s="7">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="H30" s="7">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="I30" s="17">
+        <v>2.855</v>
+      </c>
+      <c r="J30" s="17">
+        <v>3.0049999999999999</v>
+      </c>
+      <c r="K30" s="17">
+        <v>2.9820000000000002</v>
+      </c>
+      <c r="L30" s="7">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="M30" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="N30" s="7">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="O30" s="13">
         <v>600</v>
       </c>
     </row>
@@ -934,19 +1108,43 @@
       <c r="B31" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="9">
+      <c r="C31" s="19">
+        <v>2.4180000000000001</v>
+      </c>
+      <c r="D31" s="18">
+        <v>2.6030000000000002</v>
+      </c>
+      <c r="E31" s="19">
+        <v>2.5790000000000002</v>
+      </c>
+      <c r="F31" s="7">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="G31" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="H31" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="I31" s="7">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="J31" s="7">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="K31" s="7">
+        <v>9.8000000000000004E-2</v>
+      </c>
+      <c r="L31" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="M31" s="7">
+        <v>3.9E-2</v>
+      </c>
+      <c r="N31" s="7">
+        <v>3.9E-2</v>
+      </c>
+      <c r="O31" s="13">
         <v>600</v>
       </c>
     </row>
@@ -954,19 +1152,43 @@
       <c r="B32" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="12"/>
-      <c r="J32" s="12"/>
-      <c r="K32" s="12"/>
-      <c r="L32" s="12"/>
-      <c r="M32" s="12"/>
-      <c r="N32" s="12"/>
-      <c r="O32" s="9">
+      <c r="C32" s="14">
+        <v>2.25</v>
+      </c>
+      <c r="D32" s="7">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="E32" s="7">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="F32" s="7">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="G32" s="7">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="H32" s="9">
+        <v>1.6579999999999999</v>
+      </c>
+      <c r="I32" s="7">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="J32" s="7">
+        <v>4.4999999999999998E-2</v>
+      </c>
+      <c r="K32" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="L32" s="7">
+        <v>4.2000000000000003E-2</v>
+      </c>
+      <c r="M32" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="N32" s="7">
+        <v>5.0999999999999997E-2</v>
+      </c>
+      <c r="O32" s="13">
         <v>600</v>
       </c>
     </row>

--- a/experiments/20250717_more_SOBOL/iteration_0/raw_data/raw_absorbance_i0.xlsx
+++ b/experiments/20250717_more_SOBOL/iteration_0/raw_data/raw_absorbance_i0.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Surfactant\0717\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B05A833F-05BB-4A33-80B9-C8ED21D6336D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F274720-0A94-41D7-B7C0-1EF438191B8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1500" yWindow="1500" windowWidth="9528" windowHeight="10356"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="9528" windowHeight="10356"/>
   </bookViews>
   <sheets>
     <sheet name="Plate 1 - Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="MethodPointer1">2103747712</definedName>
-    <definedName name="MethodPointer2">558</definedName>
+    <definedName name="MethodPointer1">-1719727968</definedName>
+    <definedName name="MethodPointer2">608</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>Software Version</t>
   </si>
@@ -71,6 +71,9 @@
   </si>
   <si>
     <t>Reader Serial Number:</t>
+  </si>
+  <si>
+    <t>Unknown</t>
   </si>
   <si>
     <t>Reading Type</t>
@@ -172,7 +175,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -211,49 +214,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF428EC7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBAD7EF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8E9F9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFABCEEA"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBAD7EF"/>
+        <fgColor rgb="FFC9E0F4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF247CBD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3385C2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6FA9D6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60A0D1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF5197CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD8E9F9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC9E0F4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF247CBD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3385C2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF428EC7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -285,7 +300,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="19" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -313,15 +328,15 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -338,6 +353,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -710,7 +731,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="1">
-        <v>45855</v>
+        <v>45856</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -718,7 +739,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="2">
-        <v>0.64116898148148149</v>
+        <v>0.39679398148148143</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -733,72 +754,72 @@
       <c r="A10" t="s">
         <v>11</v>
       </c>
-      <c r="B10">
-        <v>24011019</v>
+      <c r="B10" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B13" s="4"/>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B19" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B21" s="4"/>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B22">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
@@ -842,60 +863,60 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C25" s="7">
         <v>4.2000000000000003E-2</v>
       </c>
       <c r="D25" s="7">
-        <v>0.16200000000000001</v>
+        <v>6.8000000000000005E-2</v>
       </c>
       <c r="E25" s="8">
-        <v>1.3720000000000001</v>
+        <v>1.2030000000000001</v>
       </c>
       <c r="F25" s="7">
-        <v>4.1000000000000002E-2</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="G25" s="7">
         <v>0.04</v>
       </c>
       <c r="H25" s="7">
-        <v>3.9E-2</v>
-      </c>
-      <c r="I25" s="8">
-        <v>1.512</v>
-      </c>
-      <c r="J25" s="8">
-        <v>1.399</v>
+        <v>0.04</v>
+      </c>
+      <c r="I25" s="9">
+        <v>1.4450000000000001</v>
+      </c>
+      <c r="J25" s="9">
+        <v>1.34</v>
       </c>
       <c r="K25" s="9">
-        <v>1.538</v>
-      </c>
-      <c r="L25" s="10">
-        <v>1.1879999999999999</v>
-      </c>
-      <c r="M25" s="11">
-        <v>0.94899999999999995</v>
-      </c>
-      <c r="N25" s="12">
-        <v>0.877</v>
-      </c>
-      <c r="O25" s="13">
+        <v>1.4370000000000001</v>
+      </c>
+      <c r="L25" s="8">
+        <v>1.2330000000000001</v>
+      </c>
+      <c r="M25" s="10">
+        <v>1.0820000000000001</v>
+      </c>
+      <c r="N25" s="10">
+        <v>1.0249999999999999</v>
+      </c>
+      <c r="O25" s="11">
         <v>600</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C26" s="14">
-        <v>2.3580000000000001</v>
-      </c>
-      <c r="D26" s="15">
-        <v>0.25700000000000001</v>
-      </c>
-      <c r="E26" s="7">
-        <v>7.4999999999999997E-2</v>
+        <v>27</v>
+      </c>
+      <c r="C26" s="12">
+        <v>2.0819999999999999</v>
+      </c>
+      <c r="D26" s="13">
+        <v>0.66400000000000003</v>
+      </c>
+      <c r="E26" s="14">
+        <v>0.23499999999999999</v>
       </c>
       <c r="F26" s="7">
         <v>0.04</v>
@@ -904,42 +925,42 @@
         <v>0.04</v>
       </c>
       <c r="H26" s="7">
-        <v>3.9E-2</v>
-      </c>
-      <c r="I26" s="12">
-        <v>0.73699999999999999</v>
-      </c>
-      <c r="J26" s="15">
-        <v>0.35099999999999998</v>
-      </c>
-      <c r="K26" s="15">
-        <v>0.42099999999999999</v>
-      </c>
-      <c r="L26" s="16">
-        <v>0.52100000000000002</v>
-      </c>
-      <c r="M26" s="16">
-        <v>0.58599999999999997</v>
-      </c>
-      <c r="N26" s="15">
-        <v>0.45300000000000001</v>
-      </c>
-      <c r="O26" s="13">
+        <v>4.7E-2</v>
+      </c>
+      <c r="I26" s="15">
+        <v>0.79800000000000004</v>
+      </c>
+      <c r="J26" s="14">
+        <v>0.39100000000000001</v>
+      </c>
+      <c r="K26" s="16">
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="L26" s="13">
+        <v>0.59399999999999997</v>
+      </c>
+      <c r="M26" s="13">
+        <v>0.67700000000000005</v>
+      </c>
+      <c r="N26" s="16">
+        <v>0.52600000000000002</v>
+      </c>
+      <c r="O26" s="11">
         <v>600</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B27" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C27" s="7">
-        <v>4.2000000000000003E-2</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="D27" s="7">
-        <v>0.17399999999999999</v>
-      </c>
-      <c r="E27" s="11">
-        <v>1.0089999999999999</v>
+        <v>0.188</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0.39800000000000002</v>
       </c>
       <c r="F27" s="7">
         <v>4.1000000000000002E-2</v>
@@ -951,39 +972,39 @@
         <v>3.9E-2</v>
       </c>
       <c r="I27" s="17">
-        <v>2.9009999999999998</v>
-      </c>
-      <c r="J27" s="17">
-        <v>2.87</v>
-      </c>
-      <c r="K27" s="18">
-        <v>2.7410000000000001</v>
+        <v>2.5750000000000002</v>
+      </c>
+      <c r="J27" s="18">
+        <v>2.2709999999999999</v>
+      </c>
+      <c r="K27" s="12">
+        <v>2.1800000000000002</v>
       </c>
       <c r="L27" s="7">
-        <v>4.2999999999999997E-2</v>
-      </c>
-      <c r="M27" s="10">
-        <v>1.3</v>
-      </c>
-      <c r="N27" s="8">
-        <v>1.3129999999999999</v>
-      </c>
-      <c r="O27" s="13">
+        <v>4.7E-2</v>
+      </c>
+      <c r="M27" s="19">
+        <v>1.589</v>
+      </c>
+      <c r="N27" s="19">
+        <v>1.5589999999999999</v>
+      </c>
+      <c r="O27" s="11">
         <v>600</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C28" s="12">
-        <v>0.82399999999999995</v>
-      </c>
-      <c r="D28" s="15">
-        <v>0.36299999999999999</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0.31900000000000001</v>
+        <v>29</v>
+      </c>
+      <c r="C28" s="10">
+        <v>0.96499999999999997</v>
+      </c>
+      <c r="D28" s="16">
+        <v>0.47299999999999998</v>
+      </c>
+      <c r="E28" s="16">
+        <v>0.48299999999999998</v>
       </c>
       <c r="F28" s="7">
         <v>0.04</v>
@@ -994,37 +1015,37 @@
       <c r="H28" s="7">
         <v>3.9E-2</v>
       </c>
-      <c r="I28" s="15">
-        <v>0.373</v>
-      </c>
-      <c r="J28" s="16">
-        <v>0.53100000000000003</v>
-      </c>
-      <c r="K28" s="12">
-        <v>0.70599999999999996</v>
-      </c>
-      <c r="L28" s="19">
-        <v>2.4009999999999998</v>
-      </c>
-      <c r="M28" s="14">
-        <v>2.2360000000000002</v>
-      </c>
-      <c r="N28" s="14">
-        <v>2.2429999999999999</v>
-      </c>
-      <c r="O28" s="13">
+      <c r="I28" s="16">
+        <v>0.45200000000000001</v>
+      </c>
+      <c r="J28" s="13">
+        <v>0.58299999999999996</v>
+      </c>
+      <c r="K28" s="15">
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="L28" s="18">
+        <v>2.335</v>
+      </c>
+      <c r="M28" s="20">
+        <v>1.849</v>
+      </c>
+      <c r="N28" s="21">
+        <v>1.873</v>
+      </c>
+      <c r="O28" s="11">
         <v>600</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C29" s="7">
         <v>0.04</v>
       </c>
       <c r="D29" s="7">
-        <v>4.2999999999999997E-2</v>
+        <v>4.2000000000000003E-2</v>
       </c>
       <c r="E29" s="7">
         <v>4.1000000000000002E-2</v>
@@ -1038,31 +1059,31 @@
       <c r="H29" s="7">
         <v>3.9E-2</v>
       </c>
-      <c r="I29" s="7">
-        <v>4.2000000000000003E-2</v>
+      <c r="I29" s="14">
+        <v>0.249</v>
       </c>
       <c r="J29" s="7">
-        <v>4.2000000000000003E-2</v>
+        <v>8.5000000000000006E-2</v>
       </c>
       <c r="K29" s="7">
-        <v>4.4999999999999998E-2</v>
-      </c>
-      <c r="L29" s="10">
-        <v>1.2470000000000001</v>
-      </c>
-      <c r="M29" s="8">
-        <v>1.3939999999999999</v>
-      </c>
-      <c r="N29" s="10">
-        <v>1.248</v>
-      </c>
-      <c r="O29" s="13">
+        <v>0.184</v>
+      </c>
+      <c r="L29" s="9">
+        <v>1.32</v>
+      </c>
+      <c r="M29" s="9">
+        <v>1.413</v>
+      </c>
+      <c r="N29" s="8">
+        <v>1.278</v>
+      </c>
+      <c r="O29" s="11">
         <v>600</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B30" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C30" s="7">
         <v>4.3999999999999997E-2</v>
@@ -1080,115 +1101,115 @@
         <v>4.2999999999999997E-2</v>
       </c>
       <c r="H30" s="7">
+        <v>0.04</v>
+      </c>
+      <c r="I30" s="18">
+        <v>2.2370000000000001</v>
+      </c>
+      <c r="J30" s="18">
+        <v>2.3530000000000002</v>
+      </c>
+      <c r="K30" s="18">
+        <v>2.355</v>
+      </c>
+      <c r="L30" s="7">
+        <v>6.8000000000000005E-2</v>
+      </c>
+      <c r="M30" s="7">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="I30" s="17">
-        <v>2.855</v>
-      </c>
-      <c r="J30" s="17">
-        <v>3.0049999999999999</v>
-      </c>
-      <c r="K30" s="17">
-        <v>2.9820000000000002</v>
-      </c>
-      <c r="L30" s="7">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="M30" s="7">
-        <v>0.04</v>
-      </c>
       <c r="N30" s="7">
-        <v>4.3999999999999997E-2</v>
-      </c>
-      <c r="O30" s="13">
+        <v>4.2999999999999997E-2</v>
+      </c>
+      <c r="O30" s="11">
         <v>600</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B31" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" s="19">
-        <v>2.4180000000000001</v>
-      </c>
-      <c r="D31" s="18">
-        <v>2.6030000000000002</v>
-      </c>
-      <c r="E31" s="19">
-        <v>2.5790000000000002</v>
+        <v>32</v>
+      </c>
+      <c r="C31" s="21">
+        <v>1.9750000000000001</v>
+      </c>
+      <c r="D31" s="12">
+        <v>2.0459999999999998</v>
+      </c>
+      <c r="E31" s="21">
+        <v>2.0139999999999998</v>
       </c>
       <c r="F31" s="7">
         <v>4.1000000000000002E-2</v>
       </c>
       <c r="G31" s="7">
-        <v>4.4999999999999998E-2</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="H31" s="7">
         <v>0.04</v>
       </c>
       <c r="I31" s="7">
-        <v>7.4999999999999997E-2</v>
+        <v>0.219</v>
       </c>
       <c r="J31" s="7">
         <v>4.2999999999999997E-2</v>
       </c>
-      <c r="K31" s="7">
-        <v>9.8000000000000004E-2</v>
+      <c r="K31" s="14">
+        <v>0.26300000000000001</v>
       </c>
       <c r="L31" s="7">
-        <v>0.04</v>
+        <v>4.5999999999999999E-2</v>
       </c>
       <c r="M31" s="7">
         <v>3.9E-2</v>
       </c>
       <c r="N31" s="7">
-        <v>3.9E-2</v>
-      </c>
-      <c r="O31" s="13">
+        <v>4.3999999999999997E-2</v>
+      </c>
+      <c r="O31" s="11">
         <v>600</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="B32" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="14">
-        <v>2.25</v>
+        <v>33</v>
+      </c>
+      <c r="C32" s="17">
+        <v>2.4089999999999998</v>
       </c>
       <c r="D32" s="7">
-        <v>4.1000000000000002E-2</v>
+        <v>4.7E-2</v>
       </c>
       <c r="E32" s="7">
         <v>4.1000000000000002E-2</v>
       </c>
-      <c r="F32" s="7">
-        <v>4.1000000000000002E-2</v>
-      </c>
-      <c r="G32" s="7">
-        <v>8.8999999999999996E-2</v>
-      </c>
-      <c r="H32" s="9">
-        <v>1.6579999999999999</v>
+      <c r="F32" s="10">
+        <v>1.044</v>
+      </c>
+      <c r="G32" s="10">
+        <v>1.018</v>
+      </c>
+      <c r="H32" s="13">
+        <v>0.76400000000000001</v>
       </c>
       <c r="I32" s="7">
-        <v>4.2000000000000003E-2</v>
+        <v>6.0999999999999999E-2</v>
       </c>
       <c r="J32" s="7">
-        <v>4.4999999999999998E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="K32" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="L32" s="7">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="M32" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="N32" s="7">
-        <v>5.0999999999999997E-2</v>
-      </c>
-      <c r="O32" s="13">
+        <v>0.184</v>
+      </c>
+      <c r="L32" s="13">
+        <v>0.747</v>
+      </c>
+      <c r="M32" s="13">
+        <v>0.71399999999999997</v>
+      </c>
+      <c r="N32" s="16">
+        <v>0.48599999999999999</v>
+      </c>
+      <c r="O32" s="11">
         <v>600</v>
       </c>
     </row>
